--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488011_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488011_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6629</v>
+        <v>6.275</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3835</v>
+        <v>5.529</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2794</v>
+        <v>0.7459</v>
       </c>
       <c r="G2" t="n">
         <v>6.1152</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6249</v>
+        <v>1.237</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6227</v>
+        <v>0.7682</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0023</v>
+        <v>0.4688</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4737</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7692</v>
+        <v>4.0376</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2176</v>
+        <v>5.6225</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4485</v>
+        <v>-1.585</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7358</v>
+        <v>3.3007</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2009</v>
+        <v>3.0158</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.465</v>
+        <v>0.2849</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5215</v>
+        <v>4.9313</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7983</v>
+        <v>3.6054</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7232</v>
+        <v>1.3259</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7857</v>
+        <v>-1.6306</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5975</v>
+        <v>-0.5896</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1882</v>
+        <v>-1.041</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4476</v>
+        <v>0.3138</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0925</v>
+        <v>0.2415</v>
       </c>
       <c r="U3" t="n">
-        <v>1.355</v>
+        <v>0.0723</v>
       </c>
       <c r="V3" t="n">
+        <v>1.8107</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.6213</v>
+      </c>
+      <c r="X3" t="n">
         <v>-1.8107</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6036</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-2.4142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5083</v>
+        <v>1.7677</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4583</v>
+        <v>2.405</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.95</v>
+        <v>-0.6373</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3007</v>
+        <v>0.6555</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0158</v>
+        <v>0.3361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2849</v>
+        <v>0.3193</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9313</v>
+        <v>2.2879</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6054</v>
+        <v>1.6009</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3259</v>
+        <v>0.6869</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6306</v>
+        <v>-1.6324</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5896</v>
+        <v>-1.2648</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.041</v>
+        <v>-0.3676</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2155</v>
+        <v>-0.4736</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0772</v>
+        <v>0.0488</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2927</v>
+        <v>-0.5224</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6213</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8107</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6271</v>
+        <v>1.4549</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6295</v>
+        <v>4.6896</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0024</v>
+        <v>-3.2347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6555</v>
+        <v>1.7358</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3361</v>
+        <v>2.2009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3193</v>
+        <v>-0.465</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2879</v>
+        <v>3.5215</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6009</v>
+        <v>2.7983</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6869</v>
+        <v>0.7232</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6324</v>
+        <v>-1.7857</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2648</v>
+        <v>-0.5975</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3676</v>
+        <v>-1.1882</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6141</v>
+        <v>1.1333</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7267</v>
+        <v>0.5645</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8874</v>
+        <v>0.5688</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6431</v>
+        <v>-0.5661</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3267</v>
+        <v>-1.917</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9699</v>
+        <v>1.3509</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2898</v>
+        <v>-0.8197</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7815</v>
+        <v>2.2776</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0713</v>
+        <v>-3.0973</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1379</v>
+        <v>-0.183</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4912</v>
+        <v>3.2088</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6467000000000001</v>
+        <v>-3.3918</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8481</v>
+        <v>-0.6367</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2727</v>
+        <v>-0.9312</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4246</v>
+        <v>0.2945</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3964</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0033</v>
+        <v>0.6322</v>
       </c>
       <c r="T6" t="n">
-        <v>0.18</v>
+        <v>0.0322</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1833</v>
+        <v>0.6</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="W6" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0817</v>
+        <v>-0.6151</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4887</v>
+        <v>0.3267</v>
       </c>
       <c r="F7" t="n">
-        <v>1.407</v>
+        <v>-0.9418</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8197</v>
+        <v>0.2898</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2776</v>
+        <v>-0.7815</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0973</v>
+        <v>1.0713</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.183</v>
+        <v>1.1379</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2088</v>
+        <v>0.4912</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.3918</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6367</v>
+        <v>-0.8481</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9312</v>
+        <v>-1.2727</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2945</v>
+        <v>0.4246</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5858</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1167</v>
+        <v>0.0247</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5395</v>
+        <v>0.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6562</v>
+        <v>-0.1552</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2071</v>
+        <v>-0.5331</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2902</v>
+        <v>-1.602</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.812</v>
+        <v>-1.4045</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4783</v>
+        <v>-0.1975</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5084</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3854</v>
+        <v>0.3029</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4368</v>
+        <v>-0.0293</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0514</v>
+        <v>0.3322</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0394</v>
+        <v>-2.5199</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1699</v>
+        <v>-1.8941</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8695</v>
+        <v>-0.6257</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5253</v>
+        <v>-2.0096</v>
       </c>
       <c r="H9" t="n">
-        <v>2.035</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.5603</v>
+        <v>-1.0293</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5934</v>
+        <v>-1.6271</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3786</v>
+        <v>-0.9882</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7852</v>
+        <v>-0.639</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1186</v>
+        <v>-0.3825</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3436</v>
+        <v>0.0078</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.775</v>
+        <v>-0.3904</v>
       </c>
       <c r="P9" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1805</v>
+        <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4353</v>
+        <v>-0.1753</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0476</v>
+        <v>-0.0688</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4829</v>
+        <v>-0.1065</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1476</v>
+        <v>-0.5331</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4142</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1125</v>
+        <v>-2.8461</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2621</v>
+        <v>0.1357</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8504</v>
+        <v>-2.9818</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0096</v>
+        <v>-1.5253</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9802999999999999</v>
+        <v>2.035</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0293</v>
+        <v>-3.5603</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6271</v>
+        <v>1.5934</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9882</v>
+        <v>4.3786</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.639</v>
+        <v>-2.7852</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3825</v>
+        <v>-3.1186</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0078</v>
+        <v>-2.3436</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3904</v>
+        <v>-0.775</v>
       </c>
       <c r="P10" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7679</v>
+        <v>0.6286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4368</v>
+        <v>0.258</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3312</v>
+        <v>0.3706</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5331</v>
+        <v>-2.1476</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5331</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7504</v>
+        <v>-3.4239</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4571</v>
+        <v>-1.3552</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2934</v>
+        <v>-2.0688</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4553</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8303</v>
+        <v>-0.5038</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.132</v>
+        <v>-0.0302</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6983</v>
+        <v>-0.4737</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4737</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.650200000000002</v>
+        <v>1.962099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8258</v>
+        <v>12.1377</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.176</v>
+        <v>-10.1758</v>
       </c>
       <c r="G12" t="n">
-        <v>5.778700000000001</v>
+        <v>5.778700000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>9.060300000000002</v>
+        <v>9.0603</v>
       </c>
       <c r="I12" t="n">
         <v>-3.281600000000001</v>
@@ -1390,10 +1390,10 @@
         <v>11.8934</v>
       </c>
       <c r="S12" t="n">
-        <v>2.808</v>
+        <v>3.1198</v>
       </c>
       <c r="T12" t="n">
-        <v>1.653</v>
+        <v>1.9649</v>
       </c>
       <c r="U12" t="n">
         <v>1.1549</v>
@@ -1402,7 +1402,7 @@
         <v>-4.9541</v>
       </c>
       <c r="W12" t="n">
-        <v>6.4984</v>
+        <v>6.498400000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-11.4525</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.656599999999999</v>
+        <v>8.1028</v>
       </c>
       <c r="E13" t="n">
-        <v>11.182</v>
+        <v>10.4689</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5254</v>
+        <v>-2.3661</v>
       </c>
       <c r="G13" t="n">
         <v>2.7144</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4684</v>
+        <v>-0.0853</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0611</v>
+        <v>0.348</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5927</v>
+        <v>-0.4333</v>
       </c>
       <c r="V13" t="n">
         <v>3.8879</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0128</v>
+        <v>2.2619</v>
       </c>
       <c r="E14" t="n">
-        <v>3.656</v>
+        <v>4.212</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6432</v>
+        <v>-1.9501</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1413</v>
+        <v>2.1487</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6496</v>
+        <v>0.0172</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4917</v>
+        <v>2.1315</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7965</v>
+        <v>4.5992</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1861</v>
+        <v>2.8923</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.7069</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6552</v>
+        <v>-2.4505</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5365</v>
+        <v>-2.8751</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1187</v>
+        <v>0.4246</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>0.717</v>
+        <v>-0.4725</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2997</v>
+        <v>-0.6715</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5826</v>
+        <v>0.199</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7403</v>
+        <v>-0.6036</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7403</v>
+        <v>1.4737</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9788</v>
+        <v>1.8844</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3971</v>
+        <v>2.1271</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4183</v>
+        <v>-0.2427</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1487</v>
+        <v>0.6766</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0172</v>
+        <v>-0.5881</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1315</v>
+        <v>1.2647</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5992</v>
+        <v>2.3296</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8923</v>
+        <v>1.7555</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7069</v>
+        <v>0.5742</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4505</v>
+        <v>-1.6531</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.8751</v>
+        <v>-2.3436</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4246</v>
+        <v>0.6905</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7557</v>
+        <v>0.1395</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4865</v>
+        <v>0.1167</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2692</v>
+        <v>0.0228</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036</v>
+        <v>0.8701</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4737</v>
+        <v>0.8701</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4994</v>
+        <v>0.9765</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2103</v>
+        <v>2.5354</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7109</v>
+        <v>-1.5589</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6766</v>
+        <v>1.1413</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5881</v>
+        <v>0.6496</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2647</v>
+        <v>0.4917</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3296</v>
+        <v>2.7965</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7555</v>
+        <v>2.1861</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5742</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6531</v>
+        <v>-1.6552</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3436</v>
+        <v>-1.5365</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6905</v>
+        <v>-0.1187</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2455</v>
+        <v>-0.3193</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8001</v>
+        <v>0.1791</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4454</v>
+        <v>-0.4984</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8701</v>
+        <v>1.7403</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8701</v>
+        <v>1.7403</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7101</v>
+        <v>-0.6082</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5029</v>
+        <v>-0.4011</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2071</v>
@@ -1780,10 +1780,10 @@
         <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1358</v>
+        <v>0.2377</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1358</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7882</v>
+        <v>-0.7705</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8461</v>
+        <v>-0.7443</v>
       </c>
       <c r="F18" t="n">
-        <v>0.058</v>
+        <v>-0.0263</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8568</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7834</v>
+        <v>-2.3243</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8731</v>
+        <v>-1.4657</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9102</v>
+        <v>-0.8587</v>
       </c>
       <c r="G19" t="n">
         <v>-5.1356</v>
@@ -1936,13 +1936,13 @@
         <v>2.3787</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7756</v>
+        <v>-0.3166</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8074</v>
+        <v>-0.3999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0318</v>
+        <v>0.0833</v>
       </c>
       <c r="V19" t="n">
         <v>1.7403</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0332</v>
+        <v>-3.6947</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3032</v>
+        <v>-2.0163</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.73</v>
+        <v>-1.6784</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8617</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.2442</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6829</v>
+        <v>-0.0302</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2227</v>
+        <v>0.2743</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4737</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0599</v>
+        <v>-5.1532</v>
       </c>
       <c r="E21" t="n">
         <v>-4.371</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6888</v>
+        <v>-0.7822</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8746</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0048</v>
+        <v>-0.0982</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3778</v>
       </c>
       <c r="U21" t="n">
-        <v>0.373</v>
+        <v>0.2797</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2272000000000007</v>
+        <v>0.6746999999999996</v>
       </c>
       <c r="E22" t="n">
-        <v>10.5491</v>
+        <v>10.345</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.7759</v>
+        <v>-9.670499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1542</v>
@@ -2170,16 +2170,16 @@
         <v>12.4882</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6219</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4794999999999998</v>
+        <v>-0.6832</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1424</v>
+        <v>-0.0368</v>
       </c>
       <c r="V22" t="n">
-        <v>4.954199999999998</v>
+        <v>4.9542</v>
       </c>
       <c r="W22" t="n">
         <v>11.4525</v>
